--- a/docs/20_基本設計/21_画面イメージ.xlsx
+++ b/docs/20_基本設計/21_画面イメージ.xlsx
@@ -19068,24 +19068,16 @@
           <t>⑨</t>
         </is>
       </c>
-      <c r="AF20" s="44" t="inlineStr">
-        <is>
-          <t>☆</t>
-        </is>
-      </c>
-      <c r="AG20" s="25" t="n"/>
+      <c r="AF20" s="18" t="inlineStr">
+        <is>
+          <t>お気に入り数　n件</t>
+        </is>
+      </c>
+      <c r="AG20" s="10" t="n"/>
       <c r="AH20" s="10" t="n"/>
       <c r="AI20" s="10" t="n"/>
-      <c r="AJ20" s="19" t="inlineStr">
-        <is>
-          <t>⑩</t>
-        </is>
-      </c>
-      <c r="AK20" s="18" t="inlineStr">
-        <is>
-          <t>n件</t>
-        </is>
-      </c>
+      <c r="AJ20" s="10" t="n"/>
+      <c r="AK20" s="10" t="n"/>
       <c r="AL20" s="10" t="n"/>
       <c r="AM20" s="10" t="n"/>
       <c r="AN20" s="10" t="n"/>
@@ -19100,7 +19092,7 @@
       <c r="C21" s="16" t="n"/>
       <c r="D21" s="19" t="inlineStr">
         <is>
-          <t>⑪</t>
+          <t>⑩</t>
         </is>
       </c>
       <c r="E21" s="45" t="inlineStr">
@@ -19158,7 +19150,7 @@
       <c r="C22" s="16" t="n"/>
       <c r="D22" s="19" t="inlineStr">
         <is>
-          <t>⑫</t>
+          <t>⑪</t>
         </is>
       </c>
       <c r="E22" s="45" t="inlineStr">
@@ -19216,7 +19208,7 @@
       <c r="C23" s="16" t="n"/>
       <c r="D23" s="19" t="inlineStr">
         <is>
-          <t>⑬</t>
+          <t>⑫</t>
         </is>
       </c>
       <c r="E23" s="45" t="inlineStr">
@@ -19412,7 +19404,7 @@
       <c r="C27" s="50" t="n"/>
       <c r="D27" s="51" t="inlineStr">
         <is>
-          <t>⑭</t>
+          <t>⑬</t>
         </is>
       </c>
       <c r="E27" s="52" t="inlineStr">
@@ -19452,7 +19444,7 @@
       <c r="AE27" s="53" t="n"/>
       <c r="AF27" s="52" t="inlineStr">
         <is>
-          <t>☆　n件</t>
+          <t>お気に入り数　n件</t>
         </is>
       </c>
       <c r="AG27" s="53" t="n"/>
@@ -19666,7 +19658,7 @@
       <c r="C32" s="10" t="n"/>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>⑮</t>
+          <t>⑭</t>
         </is>
       </c>
       <c r="E32" s="30" t="n"/>
@@ -19853,11 +19845,10 @@
       <c r="AR35" s="36" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="AE12:AM12"/>
     <mergeCell ref="E14:K14"/>
     <mergeCell ref="E10:Y10"/>
-    <mergeCell ref="AF20:AG20"/>
     <mergeCell ref="AN3:AQ3"/>
     <mergeCell ref="R12:Z12"/>
     <mergeCell ref="E12:M12"/>
@@ -20099,7 +20090,7 @@
       </c>
       <c r="C5" s="43" t="inlineStr">
         <is>
-          <t>← 戻る</t>
+          <t>← イベント一覧に戻る</t>
         </is>
       </c>
       <c r="D5" s="10" t="n"/>
@@ -20231,7 +20222,7 @@
       </c>
       <c r="AA7" s="44" t="inlineStr">
         <is>
-          <t>☆ お気に入り</t>
+          <t>☆ お気に入りに追加</t>
         </is>
       </c>
       <c r="AB7" s="24" t="n"/>
@@ -25606,13 +25597,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D88D2C49-E486-49E9-88D4-CE8EA4B73C8F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0F36675-77AF-42D9-A4C2-47B0E8EACA1F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47C485BD-1830-45B0-B6B1-E7F1204D081F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E4D89EA-1A5C-4B23-AF20-3040FC3EE911}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{744E0378-C600-49C7-86FD-EBD35AC5F48A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48A0A146-2CDE-4F86-BA20-D8782BFED01A}"/>
 </file>
--- a/docs/20_基本設計/21_画面イメージ.xlsx
+++ b/docs/20_基本設計/21_画面イメージ.xlsx
@@ -22366,12 +22366,12 @@
       <c r="AF48" s="21" t="n"/>
       <c r="AG48" s="22" t="n"/>
       <c r="AH48" s="10" t="n"/>
-      <c r="AI48" s="10" t="n"/>
-      <c r="AJ48" s="44" t="inlineStr">
-        <is>
-          <t>投稿</t>
-        </is>
-      </c>
+      <c r="AI48" s="44" t="inlineStr">
+        <is>
+          <t>返信を投稿</t>
+        </is>
+      </c>
+      <c r="AJ48" s="24" t="n"/>
       <c r="AK48" s="24" t="n"/>
       <c r="AL48" s="24" t="n"/>
       <c r="AM48" s="25" t="n"/>
@@ -22613,7 +22613,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="AJ48:AM48"/>
     <mergeCell ref="G48:AG48"/>
     <mergeCell ref="D9:P14"/>
     <mergeCell ref="F24:S24"/>
@@ -22625,6 +22624,7 @@
     <mergeCell ref="F28:M28"/>
     <mergeCell ref="AA7:AG7"/>
     <mergeCell ref="F36:AN37"/>
+    <mergeCell ref="AI48:AM48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25597,13 +25597,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0F36675-77AF-42D9-A4C2-47B0E8EACA1F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EA16337-BF7C-464C-A275-396A45B996E6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E4D89EA-1A5C-4B23-AF20-3040FC3EE911}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A89009B6-E986-4557-B6D0-0D5B5BEE7F3C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48A0A146-2CDE-4F86-BA20-D8782BFED01A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFA997A9-60FC-4E90-A070-7157186134E4}"/>
 </file>
--- a/docs/20_基本設計/21_画面イメージ.xlsx
+++ b/docs/20_基本設計/21_画面イメージ.xlsx
@@ -4632,7 +4632,7 @@
       </c>
       <c r="D9" s="26" t="inlineStr">
         <is>
-          <t>「（複製元のイベント名）」を複製しています。開催日時・申込締切を入力してください。</t>
+          <t>「（複製元のイベント名）」の内容を複写しました。開催日時・申込締切は未入力です。内容を確認のうえ入力してください。</t>
         </is>
       </c>
       <c r="E9" s="10" t="n"/>
@@ -25597,13 +25597,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EA16337-BF7C-464C-A275-396A45B996E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D4446E1-40AA-476F-AF1E-F2AB97B202BA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A89009B6-E986-4557-B6D0-0D5B5BEE7F3C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1920998D-29EC-47CC-8B9D-B693AFBA47B4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFA997A9-60FC-4E90-A070-7157186134E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5366DB73-D3BD-42C0-A704-B7B2DA934CE5}"/>
 </file>
--- a/docs/20_基本設計/21_画面イメージ.xlsx
+++ b/docs/20_基本設計/21_画面イメージ.xlsx
@@ -25597,13 +25597,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D4446E1-40AA-476F-AF1E-F2AB97B202BA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0116BF19-4A95-45E8-BFD0-27AFF07B4F55}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1920998D-29EC-47CC-8B9D-B693AFBA47B4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4505C1F6-167C-4B4B-9220-2C4D4EBD1F06}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5366DB73-D3BD-42C0-A704-B7B2DA934CE5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73266D7A-7472-4D89-ABE1-4F945AD8F08C}"/>
 </file>
--- a/docs/20_基本設計/21_画面イメージ.xlsx
+++ b/docs/20_基本設計/21_画面イメージ.xlsx
@@ -8845,7 +8845,7 @@
       <c r="AI12" s="22" t="n"/>
       <c r="AJ12" s="73" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>n%</t>
         </is>
       </c>
       <c r="AK12" s="21" t="n"/>
@@ -8911,7 +8911,7 @@
       <c r="AI13" s="22" t="n"/>
       <c r="AJ13" s="73" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>n%</t>
         </is>
       </c>
       <c r="AK13" s="21" t="n"/>
@@ -25597,13 +25597,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0116BF19-4A95-45E8-BFD0-27AFF07B4F55}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3161C064-A305-4798-B1EF-540D87F4302D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4505C1F6-167C-4B4B-9220-2C4D4EBD1F06}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D72706F0-52D0-4F65-9685-23F283E1302A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73266D7A-7472-4D89-ABE1-4F945AD8F08C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B569CAED-77F0-4198-A2E0-0D7B7B2A0DF7}"/>
 </file>